--- a/src/test/fixtures/forms-responses-http/extra-fields-export-es.xlsx
+++ b/src/test/fixtures/forms-responses-http/extra-fields-export-es.xlsx
@@ -42,7 +42,7 @@
     <x:t>Proveedores · Campo retirado</x:t>
   </x:si>
   <x:si>
-    <x:t>T807C6464-000001</x:t>
+    <x:t>TA7CABF8E-000001</x:t>
   </x:si>
   <x:si>
     <x:t>Sin información</x:t>
@@ -60,7 +60,7 @@
     <x:t>historical; historical</x:t>
   </x:si>
   <x:si>
-    <x:t>T807C6464-000002</x:t>
+    <x:t>TA7CABF8E-000002</x:t>
   </x:si>
   <x:si>
     <x:t>Primero histórico</x:t>
@@ -69,7 +69,7 @@
     <x:t>—</x:t>
   </x:si>
   <x:si>
-    <x:t>T807C6464-000003</x:t>
+    <x:t>TA7CABF8E-000003</x:t>
   </x:si>
 </x:sst>
 </file>
